--- a/debug_bbox3/layout_ranking_report.xlsx
+++ b/debug_bbox3/layout_ranking_report.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout Rankings Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relational Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +64,17 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +105,12 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -145,7 +159,19 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,27 +569,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM Layout Quality &amp; Walkability Benchmark Report</t>
+          <t xml:space="preserve">  ROOM Layout Quality &amp; Relational Accuracy Benchmark Report</t>
         </is>
       </c>
     </row>
@@ -571,7 +601,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 1  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 1  |  Metrics: Relational Accuracy, RIGHT/WRONG Relations, Furniture Overlaps, OBB Overlap Area, Out-of-Bounds, Free Floor %, Walkability</t>
         </is>
       </c>
     </row>
@@ -598,40 +628,60 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Relational Acc (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>RIGHT Relations</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>WRONG Relations</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WRONG Relation Details</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>Overlaps (Count)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>OBB Overlap (m²)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Out of Bounds</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Max OOB Dist (m)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Free Floor %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Walkable Components</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Center Clear (m)</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Grade Status</t>
         </is>
@@ -652,28 +702,42 @@
       <c r="D6" s="7" t="n">
         <v>77.25726787716954</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>None (All Relations RIGHT)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>0.0585</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>58.1</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>GOOD</t>
         </is>
@@ -681,10 +745,4188 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Detailed Spatial Relationship Verification Breakdown (RIGHT vs WRONG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Log File Name</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Source Object (s)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Relation Type</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Target Object (o)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Measurement Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>dx=-2.383m</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.355m</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.291m</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.765m</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>dz=-2.675m</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>dx=+2.576m</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>dz=+2.746m</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>dz=-0.731m</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>symmetrical to</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.554m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>taller than</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=3.69m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.34m³ vs vol_d=1.17m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=7.27m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.498m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>dist=1.640m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>dz=-2.658m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.362m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=7.27m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.34m³ vs vol_d=0.88m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.655m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.34m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>dz=+3.389m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.537m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.559m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=0.88m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=3.69m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>dist=1.585m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.638m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=3.69m³ vs vol_d=0.88m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>dx=+2.513m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>dx=+3.110m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.88m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>dz=-2.115m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>dx=+2.432m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>dist=0.997m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.726m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=0.34m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.498m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>dx=+3.194m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>dz=-3.477m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.384m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>dx=+1.551m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.391m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.88m³ vs vol_d=1.17m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>dx=+3.113m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.498m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.17m³ vs vol_d=7.27m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.618m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>dz=+3.406m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.751m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>taller than</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>dx=+1.022m</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=7.27m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.17m³ vs vol_d=3.69m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>dx=-3.191m</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>dx=+2.302m</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=7.27m³ vs vol_d=0.34m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.320m</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.303m</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>dx=-2.573m</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=0.34m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.88m³ vs vol_d=7.27m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=7.27m³ vs vol_d=3.69m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>dx=+1.640m</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=0.88m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.895m</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>dist=1.603m</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>table (5)</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.14m³ vs vol_d=3.69m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.34m³ vs vol_d=3.69m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (6)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>wardrobe (3)</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>dz=+2.086m</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.498m</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>lamp (7)</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>nightstand (2)</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.498m</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_MasterBedroom-17206.txt</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>table (8)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>shorter than</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>bed (1)</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/debug_bbox3/layout_ranking_report.xlsx
+++ b/debug_bbox3/layout_ranking_report.xlsx
@@ -19,9 +19,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,11 +70,17 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +117,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -162,7 +174,7 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +184,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -703,17 +718,17 @@
         <v>77.25726787716954</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>None (All Relations RIGHT)</t>
+          <t>lamp(7)--[above]--&gt;table(8), lamp(7)--[above]--&gt;nightstand(6), lamp(7)--[above]--&gt;table(5), lamp(7)--[above]--&gt;chair(4), lamp(7)--[above]--&gt;nightstand(2)</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -849,7 +864,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>dx=-2.383m</t>
+          <t>dx=-2.383m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -886,7 +901,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.355m</t>
+          <t>dz=-1.355m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -923,7 +938,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.291m</t>
+          <t>dz=-1.291m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -960,7 +975,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.765m</t>
+          <t>dx=-1.765m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -997,7 +1012,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>dz=-2.675m</t>
+          <t>dz=-2.675m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1049,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.51m</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1086,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>dx=+2.576m</t>
+          <t>dx=+2.576m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1123,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>dz=+2.746m</t>
+          <t>dz=+2.746m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1160,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>dz=-0.731m</t>
+          <t>dz=-0.731m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1197,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-1.56m</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1234,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>symm_dist=0.088m</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1271,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.554m</t>
+          <t>dx=-1.554m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1308,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=+0.51m</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1345,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=3.69m³</t>
+          <t>ratio=-25.53 (vol_s=0.14m³ vs vol_o=3.69m³)</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1382,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.34m³ vs vol_d=1.17m³</t>
+          <t>ratio=-2.41 (vol_s=0.34m³ vs vol_o=1.17m³)</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1419,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=7.27m³</t>
+          <t>ratio=-51.37 (vol_s=0.14m³ vs vol_o=7.27m³)</t>
         </is>
       </c>
     </row>
@@ -1434,14 +1449,14 @@
           <t>table (8)</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.498m</t>
+          <t>dy=1.498m</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1493,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>dist=1.640m</t>
+          <t>3d_dist=0.020m</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1530,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.88 (vol_s=1.17m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1604,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>dz=-2.658m</t>
+          <t>dz=-2.658m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1641,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.362m</t>
+          <t>dz=-1.362m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1678,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-2.26m</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1715,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=7.27m³</t>
+          <t>ratio=-51.37 (vol_s=0.14m³ vs vol_o=7.27m³)</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1752,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.34m³ vs vol_d=0.88m³</t>
+          <t>ratio=-1.57 (vol_s=0.34m³ vs vol_o=0.88m³)</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1826,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.655m</t>
+          <t>dz=-1.655m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1900,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.34m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.59 (vol_s=0.34m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1937,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>dz=+3.389m</t>
+          <t>dz=+3.389m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1974,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.537m</t>
+          <t>dx=-0.537m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2011,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.559m</t>
+          <t>dx=-1.559m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2048,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=0.88m³</t>
+          <t>ratio=-5.33 (vol_s=0.14m³ vs vol_o=0.88m³)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2085,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>vol_s=3.69m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.96 (vol_s=3.69m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2122,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.50m</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2159,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>dist=1.585m</t>
+          <t>3d_dist=0.128m</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2196,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>dz=+1.638m</t>
+          <t>dz=+1.638m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2233,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>vol_s=3.69m³ vs vol_d=0.88m³</t>
+          <t>ratio=+0.76 (vol_s=3.69m³ vs vol_o=0.88m³)</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2270,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>dx=+2.513m</t>
+          <t>dx=+2.513m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2307,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>dx=+3.110m</t>
+          <t>dx=+3.110m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2381,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.88m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.84 (vol_s=0.88m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2418,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.19m</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2455,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>dz=-2.115m</t>
+          <t>dz=-2.115m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2492,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>dx=+2.432m</t>
+          <t>dx=+2.432m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2529,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>dist=0.997m</t>
+          <t>3d_dist=0.161m</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2640,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.726m</t>
+          <t>dz=-1.726m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2677,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=0.34m³</t>
+          <t>ratio=-1.46 (vol_s=0.14m³ vs vol_o=0.34m³)</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2707,14 @@
           <t>nightstand (6)</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.498m</t>
+          <t>dy=1.498m</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2751,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.70m</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2788,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>dx=+3.194m</t>
+          <t>dx=+3.194m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2825,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.88 (vol_s=1.17m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2899,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>dz=-3.477m</t>
+          <t>dz=-3.477m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2936,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>dz=+1.384m</t>
+          <t>dz=+1.384m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2973,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>dx=+1.551m</t>
+          <t>dx=+1.551m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3010,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.24m</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3047,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>dz=+1.391m</t>
+          <t>dz=+1.391m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3121,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.88m³ vs vol_d=1.17m³</t>
+          <t>ratio=-0.33 (vol_s=0.88m³ vs vol_o=1.17m³)</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3195,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>dx=+3.113m</t>
+          <t>dx=+3.113m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3247,14 +3262,14 @@
           <t>table (5)</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.498m</t>
+          <t>dy=1.498m</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3306,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.17m³ vs vol_d=7.27m³</t>
+          <t>ratio=-5.23 (vol_s=1.17m³ vs vol_o=7.27m³)</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3343,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.19m</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3380,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.618m</t>
+          <t>dx=-0.618m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3417,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>dz=+3.406m</t>
+          <t>dz=+3.406m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3454,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.751m</t>
+          <t>dz=-1.751m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3491,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=+1.06m</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3528,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>dx=+1.022m</t>
+          <t>dx=+1.022m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3602,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>vol_s=7.27m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.98 (vol_s=7.27m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3639,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-1.01m</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3676,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.17m³ vs vol_d=3.69m³</t>
+          <t>ratio=-2.16 (vol_s=1.17m³ vs vol_o=3.69m³)</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3713,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-1.01m</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3750,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-2.07m</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3787,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-2.02m</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3824,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>dx=-3.191m</t>
+          <t>dx=-3.191m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3898,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>dx=+2.302m</t>
+          <t>dx=+2.302m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3935,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-2.07m</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4046,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>vol_s=7.27m³ vs vol_d=0.34m³</t>
+          <t>ratio=+0.95 (vol_s=7.27m³ vs vol_o=0.34m³)</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4120,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.320m</t>
+          <t>dz=-1.320m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4157,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.303m</t>
+          <t>dz=-1.303m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4231,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.17m³ vs vol_d=0.14m³</t>
+          <t>ratio=+0.88 (vol_s=1.17m³ vs vol_o=0.14m³)</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4268,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>dx=-2.573m</t>
+          <t>dx=-2.573m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4305,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=0.34m³</t>
+          <t>ratio=-1.46 (vol_s=0.14m³ vs vol_o=0.34m³)</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4342,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.88m³ vs vol_d=7.27m³</t>
+          <t>ratio=-7.27 (vol_s=0.88m³ vs vol_o=7.27m³)</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4379,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>vol_s=7.27m³ vs vol_d=3.69m³</t>
+          <t>ratio=+0.49 (vol_s=7.27m³ vs vol_o=3.69m³)</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4416,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>dx=+1.640m</t>
+          <t>dx=+1.640m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4453,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.46m</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4490,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=0.88m³</t>
+          <t>ratio=-5.33 (vol_s=0.14m³ vs vol_o=0.88m³)</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4527,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.895m</t>
+          <t>dx=-1.895m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4564,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-0.96m</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4601,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>dist=1.603m</t>
+          <t>3d_dist=0.141m</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4712,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.14m³ vs vol_d=3.69m³</t>
+          <t>ratio=-25.54 (vol_s=0.14m³ vs vol_o=3.69m³)</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4749,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.34m³ vs vol_d=3.69m³</t>
+          <t>ratio=-9.78 (vol_s=0.34m³ vs vol_o=3.69m³)</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4823,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>dz=+2.086m</t>
+          <t>dz=+2.086m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -4838,14 +4853,14 @@
           <t>chair (4)</t>
         </is>
       </c>
-      <c r="F113" s="12" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.498m</t>
+          <t>dy=1.498m</t>
         </is>
       </c>
     </row>
@@ -4875,14 +4890,14 @@
           <t>nightstand (2)</t>
         </is>
       </c>
-      <c r="F114" s="12" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F114" s="13" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.498m</t>
+          <t>dy=1.498m</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4934,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>height_diff=-1.20m</t>
         </is>
       </c>
     </row>
